--- a/Team-Data/2013-14/1-11-2013-14.xlsx
+++ b/Team-Data/2013-14/1-11-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
@@ -751,10 +818,10 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ2" t="n">
         <v>17</v>
@@ -793,7 +860,7 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
@@ -802,7 +869,7 @@
         <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -811,7 +878,7 @@
         <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
         <v>13</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>0.342</v>
+        <v>0.351</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>81.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K3" t="n">
         <v>0.445</v>
       </c>
       <c r="L3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S3" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T3" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U3" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X3" t="n">
         <v>4.7</v>
@@ -912,19 +979,19 @@
         <v>21.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF3" t="n">
         <v>26</v>
@@ -936,10 +1003,10 @@
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
         <v>16</v>
@@ -951,19 +1018,19 @@
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
@@ -972,7 +1039,7 @@
         <v>23</v>
       </c>
       <c r="AU3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV3" t="n">
         <v>26</v>
@@ -987,16 +1054,16 @@
         <v>10</v>
       </c>
       <c r="AZ3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC3" t="n">
         <v>22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>23</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -1025,46 +1092,46 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="n">
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>0.405</v>
+        <v>0.417</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
       </c>
       <c r="I4" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J4" t="n">
-        <v>78.2</v>
+        <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L4" t="n">
         <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O4" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="P4" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R4" t="n">
         <v>9.699999999999999</v>
@@ -1076,7 +1143,7 @@
         <v>40</v>
       </c>
       <c r="U4" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
         <v>14.6</v>
@@ -1085,34 +1152,34 @@
         <v>7.2</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.3</v>
+        <v>96.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>19</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
         <v>6</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1136,13 +1203,13 @@
         <v>10</v>
       </c>
       <c r="AO4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
@@ -1151,13 +1218,13 @@
         <v>25</v>
       </c>
       <c r="AT4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
         <v>21</v>
@@ -1169,13 +1236,13 @@
         <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>24</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" t="n">
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>0.395</v>
+        <v>0.405</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,76 +1292,76 @@
         <v>34.8</v>
       </c>
       <c r="J5" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K5" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M5" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.339</v>
+        <v>0.338</v>
       </c>
       <c r="O5" t="n">
         <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.728</v>
+        <v>0.723</v>
       </c>
       <c r="R5" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="U5" t="n">
         <v>19.4</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W5" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
         <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>16</v>
@@ -1309,7 +1376,7 @@
         <v>28</v>
       </c>
       <c r="AL5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
         <v>29</v>
@@ -1321,10 +1388,10 @@
         <v>12</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
         <v>23</v>
@@ -1336,7 +1403,7 @@
         <v>22</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>2</v>
@@ -1348,7 +1415,7 @@
         <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
         <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>0.486</v>
+        <v>0.471</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>33.8</v>
+        <v>33.6</v>
       </c>
       <c r="J6" t="n">
         <v>79.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.423</v>
+        <v>0.422</v>
       </c>
       <c r="L6" t="n">
         <v>5.3</v>
@@ -1419,37 +1486,37 @@
         <v>16.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.329</v>
+        <v>0.326</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P6" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R6" t="n">
         <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
         <v>44.9</v>
       </c>
       <c r="U6" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V6" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W6" t="n">
         <v>6.8</v>
       </c>
       <c r="X6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y6" t="n">
         <v>6.6</v>
@@ -1461,13 +1528,13 @@
         <v>21.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>91.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>15</v>
@@ -1491,13 +1558,13 @@
         <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1506,7 +1573,7 @@
         <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
         <v>8</v>
@@ -1515,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
         <v>16</v>
@@ -1527,7 +1594,7 @@
         <v>26</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>-4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF7" t="n">
         <v>24</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>23</v>
       </c>
       <c r="AG7" t="n">
         <v>24</v>
@@ -1664,10 +1731,10 @@
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1682,10 +1749,10 @@
         <v>11</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
         <v>18</v>
@@ -1703,7 +1770,7 @@
         <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW7" t="n">
         <v>22</v>
@@ -1712,7 +1779,7 @@
         <v>21</v>
       </c>
       <c r="AY7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -1753,85 +1820,85 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
         <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>0.579</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>83.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.467</v>
+        <v>0.468</v>
       </c>
       <c r="L8" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O8" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="P8" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.799</v>
+        <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="T8" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
         <v>14.1</v>
       </c>
       <c r="W8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>4.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>103</v>
+        <v>102.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1849,7 +1916,7 @@
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AK8" t="n">
         <v>4</v>
@@ -1864,10 +1931,10 @@
         <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AP8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,10 +1943,10 @@
         <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU8" t="n">
         <v>6</v>
@@ -1891,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1900,7 +1967,7 @@
         <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.528</v>
+        <v>0.514</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J9" t="n">
         <v>84.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M9" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O9" t="n">
         <v>18.6</v>
@@ -1974,46 +2041,46 @@
         <v>25.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.733</v>
+        <v>0.731</v>
       </c>
       <c r="R9" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S9" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T9" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="U9" t="n">
+        <v>22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z9" t="n">
         <v>22.3</v>
       </c>
-      <c r="V9" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="W9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>22.2</v>
-      </c>
       <c r="AA9" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.6</v>
+        <v>102.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -2028,22 +2095,22 @@
         <v>30</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
         <v>7</v>
       </c>
       <c r="AK9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" t="n">
         <v>14</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>13</v>
       </c>
       <c r="AM9" t="n">
         <v>13</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>8</v>
@@ -2058,25 +2125,25 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="n">
         <v>5</v>
       </c>
-      <c r="AT9" t="n">
-        <v>4</v>
-      </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
         <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX9" t="n">
         <v>3</v>
       </c>
       <c r="AY9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ9" t="n">
         <v>26</v>
@@ -2085,7 +2152,7 @@
         <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC9" t="n">
         <v>14</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -2117,64 +2184,64 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>0.421</v>
+        <v>0.405</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.312</v>
+        <v>0.315</v>
       </c>
       <c r="O10" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P10" t="n">
         <v>25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.662</v>
+        <v>0.661</v>
       </c>
       <c r="R10" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="U10" t="n">
-        <v>20.7</v>
+        <v>20.4</v>
       </c>
       <c r="V10" t="n">
         <v>15.5</v>
       </c>
       <c r="W10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>5.4</v>
@@ -2186,31 +2253,31 @@
         <v>20.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.1</v>
+        <v>-3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2219,10 +2286,10 @@
         <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN10" t="n">
         <v>30</v>
@@ -2243,10 +2310,10 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV10" t="n">
         <v>21</v>
@@ -2258,16 +2325,16 @@
         <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
         <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -2392,10 +2459,10 @@
         <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK11" t="n">
         <v>7</v>
@@ -2410,7 +2477,7 @@
         <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2419,7 +2486,7 @@
         <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2437,13 +2504,13 @@
         <v>14</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F12" t="n">
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.632</v>
+        <v>0.622</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,28 +2566,28 @@
         <v>37.2</v>
       </c>
       <c r="J12" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.473</v>
+        <v>0.472</v>
       </c>
       <c r="L12" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.341</v>
       </c>
       <c r="O12" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="P12" t="n">
-        <v>31.6</v>
+        <v>31.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.694</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="R12" t="n">
         <v>11</v>
@@ -2529,7 +2596,7 @@
         <v>34.3</v>
       </c>
       <c r="T12" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U12" t="n">
         <v>19.9</v>
@@ -2541,25 +2608,25 @@
         <v>7.4</v>
       </c>
       <c r="X12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.3</v>
+        <v>105.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>8</v>
@@ -2586,10 +2653,10 @@
         <v>6</v>
       </c>
       <c r="AM12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2601,16 +2668,16 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV12" t="n">
         <v>28</v>
@@ -2619,19 +2686,19 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>8.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>24</v>
@@ -2771,7 +2838,7 @@
         <v>21</v>
       </c>
       <c r="AN13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>13</v>
@@ -2801,10 +2868,10 @@
         <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3005,7 @@
         <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
@@ -2947,7 +3014,7 @@
         <v>6</v>
       </c>
       <c r="AL14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -2983,13 +3050,13 @@
         <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-5.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
@@ -3123,7 +3190,7 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
         <v>25</v>
@@ -3138,13 +3205,13 @@
         <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>22</v>
@@ -3153,13 +3220,13 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3174,10 +3241,10 @@
         <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>-1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
         <v>13</v>
@@ -3317,10 +3384,10 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP16" t="n">
         <v>23</v>
@@ -3338,7 +3405,7 @@
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3350,7 +3417,7 @@
         <v>27</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3359,7 +3426,7 @@
         <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC16" t="n">
         <v>16</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>6.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
         <v>5</v>
@@ -3481,7 +3548,7 @@
         <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
         <v>7</v>
@@ -3529,7 +3596,7 @@
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
-        <v>0.194</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
         <v>49</v>
@@ -3594,31 +3661,31 @@
         <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.42</v>
+        <v>0.421</v>
       </c>
       <c r="L18" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O18" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.772</v>
       </c>
       <c r="R18" t="n">
         <v>11.1</v>
       </c>
       <c r="S18" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T18" t="n">
         <v>41.3</v>
@@ -3627,31 +3694,31 @@
         <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W18" t="n">
         <v>7.1</v>
       </c>
       <c r="X18" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>91.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK18" t="n">
         <v>30</v>
@@ -3684,10 +3751,10 @@
         <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ18" t="n">
         <v>9</v>
@@ -3696,13 +3763,13 @@
         <v>16</v>
       </c>
       <c r="AS18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV18" t="n">
         <v>24</v>
@@ -3717,7 +3784,7 @@
         <v>19</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -3833,16 +3900,16 @@
         <v>5.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF19" t="n">
         <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
@@ -3854,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
         <v>10</v>
@@ -3881,7 +3948,7 @@
         <v>13</v>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -3937,25 +4004,25 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" t="n">
         <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.417</v>
+        <v>0.429</v>
       </c>
       <c r="H20" t="n">
         <v>48.6</v>
       </c>
       <c r="I20" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J20" t="n">
-        <v>85.5</v>
+        <v>85.8</v>
       </c>
       <c r="K20" t="n">
         <v>0.456</v>
@@ -3967,91 +4034,91 @@
         <v>16.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O20" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.765</v>
       </c>
       <c r="R20" t="n">
         <v>12.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U20" t="n">
         <v>22.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W20" t="n">
         <v>8.5</v>
       </c>
       <c r="X20" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.6</v>
+        <v>101.4</v>
       </c>
       <c r="AC20" t="n">
         <v>-1.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF20" t="n">
         <v>18</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH20" t="n">
         <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
@@ -4060,10 +4127,10 @@
         <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AU20" t="n">
         <v>11</v>
@@ -4072,22 +4139,22 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA20" t="n">
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC20" t="n">
         <v>17</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -4119,46 +4186,46 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.389</v>
+        <v>0.371</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J21" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.437</v>
+        <v>0.436</v>
       </c>
       <c r="L21" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.357</v>
+        <v>0.358</v>
       </c>
       <c r="O21" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="P21" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R21" t="n">
         <v>10.6</v>
@@ -4170,46 +4237,46 @@
         <v>39.5</v>
       </c>
       <c r="U21" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V21" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W21" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X21" t="n">
         <v>4.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.7</v>
+        <v>-3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
@@ -4218,7 +4285,7 @@
         <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
         <v>7</v>
@@ -4227,7 +4294,7 @@
         <v>7</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4248,19 +4315,19 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY21" t="n">
         <v>6</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>5</v>
       </c>
       <c r="AZ21" t="n">
         <v>28</v>
@@ -4269,10 +4336,10 @@
         <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -4301,37 +4368,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F22" t="n">
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0.757</v>
+        <v>0.75</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J22" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.465</v>
+        <v>0.467</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O22" t="n">
         <v>21.1</v>
@@ -4340,19 +4407,19 @@
         <v>25.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="S22" t="n">
         <v>35.9</v>
       </c>
       <c r="T22" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V22" t="n">
         <v>15.6</v>
@@ -4367,22 +4434,22 @@
         <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.2</v>
+        <v>105.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4391,13 +4458,13 @@
         <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4409,7 +4476,7 @@
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
@@ -4421,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
@@ -4430,28 +4497,28 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW22" t="n">
         <v>12</v>
       </c>
       <c r="AX22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
       </c>
       <c r="BB22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -4483,19 +4550,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
       </c>
       <c r="F23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>0.27</v>
+        <v>0.278</v>
       </c>
       <c r="H23" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I23" t="n">
         <v>36.1</v>
@@ -4507,13 +4574,13 @@
         <v>0.437</v>
       </c>
       <c r="L23" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M23" t="n">
         <v>21.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.345</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
         <v>15.9</v>
@@ -4522,7 +4589,7 @@
         <v>21.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R23" t="n">
         <v>9.6</v>
@@ -4531,16 +4598,16 @@
         <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.2</v>
       </c>
       <c r="V23" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W23" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
         <v>4.3</v>
@@ -4552,22 +4619,22 @@
         <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.7</v>
+        <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
       </c>
       <c r="AF23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG23" t="n">
         <v>29</v>
@@ -4579,25 +4646,25 @@
         <v>23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
         <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM23" t="n">
         <v>15</v>
       </c>
       <c r="AN23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP23" t="n">
         <v>21</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>20</v>
       </c>
       <c r="AQ23" t="n">
         <v>19</v>
@@ -4609,10 +4676,10 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="n">
         <v>15</v>
@@ -4624,13 +4691,13 @@
         <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -4665,55 +4732,55 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>0.324</v>
+        <v>0.333</v>
       </c>
       <c r="H24" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I24" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="J24" t="n">
-        <v>88.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M24" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O24" t="n">
         <v>16.4</v>
       </c>
       <c r="P24" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0.717</v>
       </c>
       <c r="R24" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S24" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="T24" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="U24" t="n">
         <v>22.9</v>
@@ -4725,25 +4792,25 @@
         <v>9</v>
       </c>
       <c r="X24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA24" t="n">
         <v>20.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>102.5</v>
+        <v>102.8</v>
       </c>
       <c r="AC24" t="n">
         <v>-8.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>26</v>
@@ -4773,7 +4840,7 @@
         <v>11</v>
       </c>
       <c r="AN24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO24" t="n">
         <v>18</v>
@@ -4785,13 +4852,13 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
         <v>8</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>9</v>
@@ -4803,19 +4870,19 @@
         <v>4</v>
       </c>
       <c r="AX24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
       </c>
       <c r="BB24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
         <v>21</v>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>0.583</v>
+        <v>0.6</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
       </c>
       <c r="I25" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J25" t="n">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="N25" t="n">
         <v>0.369</v>
       </c>
       <c r="O25" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P25" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.748</v>
+        <v>0.745</v>
       </c>
       <c r="R25" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
         <v>43.2</v>
       </c>
       <c r="U25" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V25" t="n">
         <v>15.3</v>
@@ -4907,10 +4974,10 @@
         <v>8.6</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z25" t="n">
         <v>21.4</v>
@@ -4919,19 +4986,19 @@
         <v>20.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG25" t="n">
         <v>9</v>
@@ -4943,7 +5010,7 @@
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>11</v>
@@ -4952,7 +5019,7 @@
         <v>2</v>
       </c>
       <c r="AM25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN25" t="n">
         <v>8</v>
@@ -4961,13 +5028,13 @@
         <v>15</v>
       </c>
       <c r="AP25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR25" t="n">
         <v>13</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>12</v>
       </c>
       <c r="AS25" t="n">
         <v>17</v>
@@ -4979,10 +5046,10 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -4991,7 +5058,7 @@
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.757</v>
+        <v>0.75</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,46 +5114,46 @@
         <v>40.2</v>
       </c>
       <c r="J26" t="n">
-        <v>88.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
         <v>10.3</v>
       </c>
       <c r="M26" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.396</v>
+        <v>0.395</v>
       </c>
       <c r="O26" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q26" t="n">
         <v>0.821</v>
       </c>
       <c r="R26" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="T26" t="n">
         <v>46.6</v>
       </c>
       <c r="U26" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V26" t="n">
         <v>13.9</v>
       </c>
       <c r="W26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X26" t="n">
         <v>4.8</v>
@@ -5095,7 +5162,7 @@
         <v>3.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA26" t="n">
         <v>20.2</v>
@@ -5104,13 +5171,13 @@
         <v>109.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="n">
         <v>3</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5143,7 +5210,7 @@
         <v>10</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-3</v>
       </c>
       <c r="AD27" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
       </c>
       <c r="AF27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG27" t="n">
         <v>25</v>
@@ -5310,19 +5377,19 @@
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN27" t="n">
         <v>25</v>
       </c>
       <c r="AO27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
         <v>6</v>
@@ -5340,7 +5407,7 @@
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
@@ -5358,13 +5425,13 @@
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5510,22 +5577,22 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW28" t="n">
         <v>15</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -5575,58 +5642,58 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
         <v>17</v>
       </c>
       <c r="G29" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
       </c>
       <c r="I29" t="n">
-        <v>35.7</v>
+        <v>35.9</v>
       </c>
       <c r="J29" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L29" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M29" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="N29" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
       <c r="O29" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P29" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R29" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S29" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T29" t="n">
-        <v>42.9</v>
+        <v>42.7</v>
       </c>
       <c r="U29" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V29" t="n">
         <v>14.6</v>
@@ -5638,25 +5705,25 @@
         <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
         <v>22.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>98.7</v>
+        <v>98.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
         <v>11</v>
@@ -5683,19 +5750,19 @@
         <v>12</v>
       </c>
       <c r="AN29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO29" t="n">
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
       </c>
       <c r="AR29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
@@ -5707,13 +5774,13 @@
         <v>26</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AW29" t="n">
         <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
@@ -5722,7 +5789,7 @@
         <v>29</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -5853,10 +5920,10 @@
         <v>26</v>
       </c>
       <c r="AJ30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="n">
         <v>24</v>
@@ -5868,16 +5935,16 @@
         <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS30" t="n">
         <v>28</v>
@@ -5886,10 +5953,10 @@
         <v>26</v>
       </c>
       <c r="AU30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
         <v>25</v>
@@ -5901,7 +5968,7 @@
         <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>14</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
@@ -5939,64 +6006,64 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E31" t="n">
         <v>16</v>
       </c>
       <c r="F31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G31" t="n">
-        <v>0.457</v>
+        <v>0.471</v>
       </c>
       <c r="H31" t="n">
         <v>48.9</v>
       </c>
       <c r="I31" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J31" t="n">
-        <v>84.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L31" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P31" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R31" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="S31" t="n">
         <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U31" t="n">
         <v>22.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.6</v>
@@ -6005,28 +6072,28 @@
         <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AB31" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
@@ -6035,22 +6102,22 @@
         <v>17</v>
       </c>
       <c r="AJ31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AM31" t="n">
         <v>17</v>
       </c>
       <c r="AN31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP31" t="n">
         <v>26</v>
@@ -6059,34 +6126,34 @@
         <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS31" t="n">
         <v>19</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>10</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
         <v>18</v>
       </c>
       <c r="AY31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-11-2013-14</t>
+          <t>2014-01-11</t>
         </is>
       </c>
     </row>
